--- a/part_numbers_db.xlsx
+++ b/part_numbers_db.xlsx
@@ -12,6 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier2_Suppliers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component_Materials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMS_Providers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributors" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part_Distributors" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt_Sources" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier_Profiles" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5876,6 +5881,67 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supplier_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Supplier_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Fab</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_Fab_Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Wafer_Source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Key_Materials_Override</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Created_at</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Updated_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6994,4 +7060,253 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EMS_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>EMS_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Financial_Health</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Capacity_Utilization_Pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Certifications</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Backup_Sites_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Years_Business</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Created_at</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Updated_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Distributor_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Financial_Health</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lead_Time_Markup_Weeks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stock_Level_Weeks_Coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Certifications</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Backup_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Created_at</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Updated_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Part_Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distributor_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Allocation_Pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Created_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Part_Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Supplier_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Frontend_Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Backend_Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lead_Time_Weeks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Financial_Health</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Qualification_Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Allocation_Pct</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Created_at</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>